--- a/artfynd/A 16092-2024 artfynd.xlsx
+++ b/artfynd/A 16092-2024 artfynd.xlsx
@@ -5358,10 +5358,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117995604</v>
+        <v>117996068</v>
       </c>
       <c r="B45" t="n">
-        <v>97870</v>
+        <v>56491</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5370,38 +5370,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219874</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>762955</v>
+        <v>762952</v>
       </c>
       <c r="R45" t="n">
-        <v>7308825</v>
+        <v>7308740</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5448,19 +5448,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117995608</v>
+        <v>117995604</v>
       </c>
       <c r="B46" t="n">
         <v>97870</v>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>762928</v>
+        <v>762955</v>
       </c>
       <c r="R46" t="n">
-        <v>7308793</v>
+        <v>7308825</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5562,10 +5562,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117996068</v>
+        <v>117995608</v>
       </c>
       <c r="B47" t="n">
-        <v>56491</v>
+        <v>97870</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5574,38 +5574,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>219874</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>762952</v>
+        <v>762928</v>
       </c>
       <c r="R47" t="n">
-        <v>7308740</v>
+        <v>7308793</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5652,12 +5652,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117996041</v>
+        <v>117996064</v>
       </c>
       <c r="B57" t="n">
-        <v>97857</v>
+        <v>97836</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6597,25 +6597,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>762896</v>
+        <v>762909</v>
       </c>
       <c r="R57" t="n">
-        <v>7308661</v>
+        <v>7308662</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6687,7 +6687,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117996064</v>
+        <v>117995635</v>
       </c>
       <c r="B58" t="n">
         <v>97836</v>
@@ -6723,14 +6723,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>762909</v>
+        <v>762962</v>
       </c>
       <c r="R58" t="n">
-        <v>7308662</v>
+        <v>7308672</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6777,22 +6777,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117995635</v>
+        <v>117996041</v>
       </c>
       <c r="B59" t="n">
-        <v>97836</v>
+        <v>97857</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6801,38 +6801,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>762962</v>
+        <v>762896</v>
       </c>
       <c r="R59" t="n">
-        <v>7308672</v>
+        <v>7308661</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6879,12 +6879,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 16092-2024 artfynd.xlsx
+++ b/artfynd/A 16092-2024 artfynd.xlsx
@@ -1277,7 +1277,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117646835</v>
+        <v>117646738</v>
       </c>
       <c r="B7" t="n">
         <v>97836</v>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762967</v>
+        <v>762979</v>
       </c>
       <c r="R7" t="n">
-        <v>7308415</v>
+        <v>7308557</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117646699</v>
+        <v>117646835</v>
       </c>
       <c r="B8" t="n">
         <v>97836</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762936</v>
+        <v>762967</v>
       </c>
       <c r="R8" t="n">
-        <v>7308406</v>
+        <v>7308415</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117646766</v>
+        <v>117646676</v>
       </c>
       <c r="B10" t="n">
         <v>97836</v>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762890</v>
+        <v>762976</v>
       </c>
       <c r="R10" t="n">
-        <v>7308462</v>
+        <v>7308680</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1737,7 +1737,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117646676</v>
+        <v>117646766</v>
       </c>
       <c r="B11" t="n">
         <v>97836</v>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762976</v>
+        <v>762890</v>
       </c>
       <c r="R11" t="n">
-        <v>7308680</v>
+        <v>7308462</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117646738</v>
+        <v>117646699</v>
       </c>
       <c r="B12" t="n">
         <v>97836</v>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762979</v>
+        <v>762936</v>
       </c>
       <c r="R12" t="n">
-        <v>7308557</v>
+        <v>7308406</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117664470</v>
+        <v>117666782</v>
       </c>
       <c r="B13" t="n">
-        <v>97754</v>
+        <v>57169</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,38 +1979,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223591</v>
+        <v>100011</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762765</v>
+        <v>762791</v>
       </c>
       <c r="R13" t="n">
-        <v>7308648</v>
+        <v>7308597</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2040,40 +2052,49 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117663042</v>
+        <v>117664464</v>
       </c>
       <c r="B14" t="n">
-        <v>90648</v>
+        <v>79590</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,41 +2103,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>762726</v>
+        <v>762992</v>
       </c>
       <c r="R14" t="n">
-        <v>7308406</v>
+        <v>7308570</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2157,7 +2175,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2176,10 +2193,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117661434</v>
+        <v>117661399</v>
       </c>
       <c r="B15" t="n">
-        <v>82259</v>
+        <v>78481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,29 +2209,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>230405</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2223,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>762980</v>
+        <v>762825</v>
       </c>
       <c r="R15" t="n">
-        <v>7308629</v>
+        <v>7308431</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2274,22 +2287,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117667686</v>
+        <v>117664449</v>
       </c>
       <c r="B16" t="n">
-        <v>57303</v>
+        <v>90425</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,42 +2315,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762976</v>
+        <v>762801</v>
       </c>
       <c r="R16" t="n">
-        <v>7308367</v>
+        <v>7308448</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2372,11 +2377,6 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2389,22 +2389,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117664467</v>
+        <v>117664476</v>
       </c>
       <c r="B17" t="n">
-        <v>79590</v>
+        <v>97870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>762934</v>
+        <v>762925</v>
       </c>
       <c r="R17" t="n">
-        <v>7308414</v>
+        <v>7308714</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117664465</v>
+        <v>117664474</v>
       </c>
       <c r="B18" t="n">
-        <v>79590</v>
+        <v>97870</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2519,21 +2519,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>762925</v>
+        <v>762947</v>
       </c>
       <c r="R18" t="n">
-        <v>7308403</v>
+        <v>7308669</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117664471</v>
+        <v>117663055</v>
       </c>
       <c r="B19" t="n">
-        <v>97754</v>
+        <v>57287</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,38 +2617,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223591</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>762933</v>
+        <v>763011</v>
       </c>
       <c r="R19" t="n">
-        <v>7308409</v>
+        <v>7308585</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2683,35 +2687,39 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117663055</v>
+        <v>117664472</v>
       </c>
       <c r="B20" t="n">
-        <v>57287</v>
+        <v>79465</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,42 +2728,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>763011</v>
+        <v>762951</v>
       </c>
       <c r="R20" t="n">
-        <v>7308585</v>
+        <v>7308667</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2790,11 +2794,6 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2807,19 +2806,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117664476</v>
+        <v>117664475</v>
       </c>
       <c r="B21" t="n">
         <v>97870</v>
@@ -2859,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>762925</v>
+        <v>762938</v>
       </c>
       <c r="R21" t="n">
-        <v>7308714</v>
+        <v>7308665</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2921,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117664472</v>
+        <v>117664470</v>
       </c>
       <c r="B22" t="n">
-        <v>79465</v>
+        <v>97754</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>223591</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2961,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>762951</v>
+        <v>762765</v>
       </c>
       <c r="R22" t="n">
-        <v>7308667</v>
+        <v>7308648</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3005,6 +3004,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117664469</v>
+        <v>117664471</v>
       </c>
       <c r="B23" t="n">
         <v>97754</v>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>762937</v>
+        <v>762933</v>
       </c>
       <c r="R23" t="n">
-        <v>7308671</v>
+        <v>7308409</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3107,6 +3107,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3125,10 +3126,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117664474</v>
+        <v>117663042</v>
       </c>
       <c r="B24" t="n">
-        <v>97870</v>
+        <v>90648</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3137,38 +3138,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>762947</v>
+        <v>762726</v>
       </c>
       <c r="R24" t="n">
-        <v>7308669</v>
+        <v>7308406</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3209,6 +3213,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3227,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117645796</v>
+        <v>117664457</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>56499</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3239,39 +3244,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3279,10 +3276,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>762953</v>
+        <v>762798</v>
       </c>
       <c r="R25" t="n">
-        <v>7308667</v>
+        <v>7308440</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3317,35 +3314,39 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117664457</v>
+        <v>117664477</v>
       </c>
       <c r="B26" t="n">
-        <v>56499</v>
+        <v>97870</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3358,38 +3359,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>762798</v>
+        <v>762877</v>
       </c>
       <c r="R26" t="n">
-        <v>7308440</v>
+        <v>7308488</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3424,11 +3421,6 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3446,17 +3438,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117664475</v>
+        <v>117667686</v>
       </c>
       <c r="B27" t="n">
-        <v>97870</v>
+        <v>57303</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3465,38 +3457,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>762938</v>
+        <v>762976</v>
       </c>
       <c r="R27" t="n">
-        <v>7308665</v>
+        <v>7308367</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3531,6 +3531,11 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3543,22 +3548,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117664477</v>
+        <v>117664473</v>
       </c>
       <c r="B28" t="n">
-        <v>97870</v>
+        <v>97725</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3567,25 +3572,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219874</v>
+        <v>233</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3595,10 +3600,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>762877</v>
+        <v>762931</v>
       </c>
       <c r="R28" t="n">
-        <v>7308488</v>
+        <v>7308402</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3657,10 +3662,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117646899</v>
+        <v>117664467</v>
       </c>
       <c r="B29" t="n">
-        <v>97836</v>
+        <v>79590</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3669,50 +3674,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>762982</v>
+        <v>762934</v>
       </c>
       <c r="R29" t="n">
-        <v>7308684</v>
+        <v>7308414</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3753,29 +3746,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117666782</v>
+        <v>117646899</v>
       </c>
       <c r="B30" t="n">
-        <v>57169</v>
+        <v>97836</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3784,39 +3776,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100011</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3824,10 +3816,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>762791</v>
+        <v>762982</v>
       </c>
       <c r="R30" t="n">
-        <v>7308597</v>
+        <v>7308684</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3857,49 +3849,40 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117659961</v>
+        <v>117646797</v>
       </c>
       <c r="B31" t="n">
-        <v>78217</v>
+        <v>97836</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3908,34 +3891,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3943,10 +3931,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>762953</v>
+        <v>763000</v>
       </c>
       <c r="R31" t="n">
-        <v>7308413</v>
+        <v>7308589</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3994,22 +3982,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117661399</v>
+        <v>117645796</v>
       </c>
       <c r="B32" t="n">
-        <v>78481</v>
+        <v>97836</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4018,30 +4006,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4049,10 +4046,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>762825</v>
+        <v>762953</v>
       </c>
       <c r="R32" t="n">
-        <v>7308431</v>
+        <v>7308667</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4105,17 +4102,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117646797</v>
+        <v>117659873</v>
       </c>
       <c r="B33" t="n">
-        <v>97836</v>
+        <v>78216</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4124,39 +4121,34 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4164,10 +4156,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>763000</v>
+        <v>762765</v>
       </c>
       <c r="R33" t="n">
-        <v>7308589</v>
+        <v>7308409</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4215,22 +4207,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117664464</v>
+        <v>117661434</v>
       </c>
       <c r="B34" t="n">
-        <v>79590</v>
+        <v>82259</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4239,38 +4231,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>762992</v>
+        <v>762980</v>
       </c>
       <c r="R34" t="n">
-        <v>7308570</v>
+        <v>7308629</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4311,6 +4310,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117664449</v>
+        <v>117664465</v>
       </c>
       <c r="B35" t="n">
-        <v>90425</v>
+        <v>79590</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4341,25 +4341,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>762801</v>
+        <v>762925</v>
       </c>
       <c r="R35" t="n">
-        <v>7308448</v>
+        <v>7308403</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4431,10 +4431,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117659873</v>
+        <v>117659961</v>
       </c>
       <c r="B36" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4447,21 +4447,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>762765</v>
+        <v>762953</v>
       </c>
       <c r="R36" t="n">
-        <v>7308409</v>
+        <v>7308413</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4541,10 +4541,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117664473</v>
+        <v>117664469</v>
       </c>
       <c r="B37" t="n">
-        <v>97725</v>
+        <v>97754</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4553,25 +4553,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>233</v>
+        <v>223591</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>762931</v>
+        <v>762937</v>
       </c>
       <c r="R37" t="n">
-        <v>7308402</v>
+        <v>7308671</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4643,10 +4643,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117996055</v>
+        <v>117996065</v>
       </c>
       <c r="B38" t="n">
-        <v>79597</v>
+        <v>97836</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4655,25 +4655,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4683,10 +4683,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>762931</v>
+        <v>762908</v>
       </c>
       <c r="R38" t="n">
-        <v>7308827</v>
+        <v>7308658</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4745,10 +4745,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117996046</v>
+        <v>117996057</v>
       </c>
       <c r="B39" t="n">
-        <v>97754</v>
+        <v>97836</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4757,25 +4757,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>762949</v>
+        <v>763015</v>
       </c>
       <c r="R39" t="n">
-        <v>7308733</v>
+        <v>7308599</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117995646</v>
+        <v>117995631</v>
       </c>
       <c r="B40" t="n">
-        <v>97753</v>
+        <v>97836</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4860,25 +4860,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117995606</v>
+        <v>117995634</v>
       </c>
       <c r="B41" t="n">
-        <v>97870</v>
+        <v>97836</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4962,25 +4962,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>762892</v>
+        <v>762899</v>
       </c>
       <c r="R41" t="n">
-        <v>7308626</v>
+        <v>7308644</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117996065</v>
+        <v>117996037</v>
       </c>
       <c r="B42" t="n">
-        <v>97836</v>
+        <v>79590</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5064,25 +5064,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>762908</v>
+        <v>762933</v>
       </c>
       <c r="R42" t="n">
-        <v>7308658</v>
+        <v>7308827</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5154,7 +5154,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117995631</v>
+        <v>117995633</v>
       </c>
       <c r="B43" t="n">
         <v>97836</v>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>762898</v>
+        <v>762884</v>
       </c>
       <c r="R43" t="n">
-        <v>7308634</v>
+        <v>7308624</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5256,10 +5256,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117996049</v>
+        <v>117996052</v>
       </c>
       <c r="B44" t="n">
-        <v>97838</v>
+        <v>97870</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5272,21 +5272,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219811</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>762954</v>
+        <v>762974</v>
       </c>
       <c r="R44" t="n">
-        <v>7308830</v>
+        <v>7308742</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117996068</v>
+        <v>117996070</v>
       </c>
       <c r="B45" t="n">
-        <v>56491</v>
+        <v>97754</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5370,25 +5370,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>223591</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>762952</v>
+        <v>762942</v>
       </c>
       <c r="R45" t="n">
-        <v>7308740</v>
+        <v>7308749</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5442,6 +5442,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5460,10 +5461,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117995604</v>
+        <v>117996043</v>
       </c>
       <c r="B46" t="n">
-        <v>97870</v>
+        <v>57303</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5472,38 +5473,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>762955</v>
+        <v>762976</v>
       </c>
       <c r="R46" t="n">
-        <v>7308825</v>
+        <v>7308712</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5550,19 +5551,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117995608</v>
+        <v>117995606</v>
       </c>
       <c r="B47" t="n">
         <v>97870</v>
@@ -5602,10 +5603,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>762928</v>
+        <v>762892</v>
       </c>
       <c r="R47" t="n">
-        <v>7308793</v>
+        <v>7308626</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5664,10 +5665,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117995607</v>
+        <v>117996049</v>
       </c>
       <c r="B48" t="n">
-        <v>97870</v>
+        <v>97838</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5680,34 +5681,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219874</v>
+        <v>219811</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>762982</v>
+        <v>762954</v>
       </c>
       <c r="R48" t="n">
-        <v>7308743</v>
+        <v>7308830</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5754,22 +5755,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117996052</v>
+        <v>117995630</v>
       </c>
       <c r="B49" t="n">
-        <v>97870</v>
+        <v>97836</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5778,38 +5779,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>762974</v>
+        <v>763021</v>
       </c>
       <c r="R49" t="n">
-        <v>7308742</v>
+        <v>7308620</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -5856,22 +5857,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117996040</v>
+        <v>117995608</v>
       </c>
       <c r="B50" t="n">
-        <v>97857</v>
+        <v>97870</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5884,16 +5885,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5904,14 +5905,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>762910</v>
+        <v>762928</v>
       </c>
       <c r="R50" t="n">
-        <v>7308657</v>
+        <v>7308793</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -5958,22 +5959,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117996047</v>
+        <v>117995635</v>
       </c>
       <c r="B51" t="n">
-        <v>97754</v>
+        <v>97836</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5982,38 +5983,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>762937</v>
+        <v>762962</v>
       </c>
       <c r="R51" t="n">
-        <v>7308759</v>
+        <v>7308672</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6054,29 +6055,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117996037</v>
+        <v>117996047</v>
       </c>
       <c r="B52" t="n">
-        <v>79590</v>
+        <v>97754</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>223591</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>762933</v>
+        <v>762937</v>
       </c>
       <c r="R52" t="n">
-        <v>7308827</v>
+        <v>7308759</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6157,6 +6157,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6175,10 +6176,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117996057</v>
+        <v>117995646</v>
       </c>
       <c r="B53" t="n">
-        <v>97836</v>
+        <v>97753</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6187,38 +6188,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>763015</v>
+        <v>762898</v>
       </c>
       <c r="R53" t="n">
-        <v>7308599</v>
+        <v>7308634</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6259,29 +6260,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117995630</v>
+        <v>117996041</v>
       </c>
       <c r="B54" t="n">
-        <v>97836</v>
+        <v>97857</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6290,38 +6290,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>763021</v>
+        <v>762896</v>
       </c>
       <c r="R54" t="n">
-        <v>7308620</v>
+        <v>7308661</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6368,22 +6368,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117995634</v>
+        <v>117995607</v>
       </c>
       <c r="B55" t="n">
-        <v>97836</v>
+        <v>97870</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6392,25 +6392,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>762899</v>
+        <v>762982</v>
       </c>
       <c r="R55" t="n">
-        <v>7308644</v>
+        <v>7308743</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117996070</v>
+        <v>117996036</v>
       </c>
       <c r="B56" t="n">
-        <v>97754</v>
+        <v>90499</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6494,25 +6494,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>223591</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>762942</v>
+        <v>762963</v>
       </c>
       <c r="R56" t="n">
-        <v>7308749</v>
+        <v>7308745</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -6566,7 +6566,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6585,10 +6584,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117996064</v>
+        <v>117996046</v>
       </c>
       <c r="B57" t="n">
-        <v>97836</v>
+        <v>97754</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6597,25 +6596,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6625,10 +6624,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>762909</v>
+        <v>762949</v>
       </c>
       <c r="R57" t="n">
-        <v>7308662</v>
+        <v>7308733</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6669,6 +6668,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6687,7 +6687,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117995635</v>
+        <v>117996063</v>
       </c>
       <c r="B58" t="n">
         <v>97836</v>
@@ -6723,14 +6723,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>762962</v>
+        <v>762979</v>
       </c>
       <c r="R58" t="n">
-        <v>7308672</v>
+        <v>7308612</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6777,22 +6777,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117996041</v>
+        <v>117996055</v>
       </c>
       <c r="B59" t="n">
-        <v>97857</v>
+        <v>79597</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6805,21 +6805,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>762896</v>
+        <v>762931</v>
       </c>
       <c r="R59" t="n">
-        <v>7308661</v>
+        <v>7308827</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117995633</v>
+        <v>117996068</v>
       </c>
       <c r="B60" t="n">
-        <v>97836</v>
+        <v>56491</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6903,38 +6903,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>762884</v>
+        <v>762952</v>
       </c>
       <c r="R60" t="n">
-        <v>7308624</v>
+        <v>7308740</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -6981,22 +6981,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117996036</v>
+        <v>117995604</v>
       </c>
       <c r="B61" t="n">
-        <v>90499</v>
+        <v>97870</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7005,38 +7005,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>762963</v>
+        <v>762955</v>
       </c>
       <c r="R61" t="n">
-        <v>7308745</v>
+        <v>7308825</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7083,22 +7083,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117996043</v>
+        <v>117996064</v>
       </c>
       <c r="B62" t="n">
-        <v>57303</v>
+        <v>97836</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7107,25 +7107,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>762976</v>
+        <v>762909</v>
       </c>
       <c r="R62" t="n">
-        <v>7308712</v>
+        <v>7308662</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7197,10 +7197,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117996063</v>
+        <v>117996040</v>
       </c>
       <c r="B63" t="n">
-        <v>97836</v>
+        <v>97857</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7209,25 +7209,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>762979</v>
+        <v>762910</v>
       </c>
       <c r="R63" t="n">
-        <v>7308612</v>
+        <v>7308657</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>

--- a/artfynd/A 16092-2024 artfynd.xlsx
+++ b/artfynd/A 16092-2024 artfynd.xlsx
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117646738</v>
+        <v>117646835</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762979</v>
+        <v>762967</v>
       </c>
       <c r="R7" t="n">
-        <v>7308557</v>
+        <v>7308415</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117646835</v>
+        <v>117646766</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762967</v>
+        <v>762890</v>
       </c>
       <c r="R8" t="n">
-        <v>7308415</v>
+        <v>7308462</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117646870</v>
+        <v>117646738</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762973</v>
+        <v>762979</v>
       </c>
       <c r="R9" t="n">
-        <v>7308555</v>
+        <v>7308557</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117646676</v>
+        <v>117646699</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762976</v>
+        <v>762936</v>
       </c>
       <c r="R10" t="n">
-        <v>7308680</v>
+        <v>7308406</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117646766</v>
+        <v>117646676</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762890</v>
+        <v>762976</v>
       </c>
       <c r="R11" t="n">
-        <v>7308462</v>
+        <v>7308680</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117646699</v>
+        <v>117646870</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762936</v>
+        <v>762973</v>
       </c>
       <c r="R12" t="n">
-        <v>7308406</v>
+        <v>7308555</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117666782</v>
+        <v>117664449</v>
       </c>
       <c r="B13" t="n">
-        <v>57169</v>
+        <v>90427</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,46 +1983,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100011</v>
+        <v>3242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762791</v>
+        <v>762801</v>
       </c>
       <c r="R13" t="n">
-        <v>7308597</v>
+        <v>7308448</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2052,19 +2040,9 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,22 +2057,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117664464</v>
+        <v>117661434</v>
       </c>
       <c r="B14" t="n">
-        <v>79590</v>
+        <v>82261</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,38 +2081,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>762992</v>
+        <v>762980</v>
       </c>
       <c r="R14" t="n">
-        <v>7308570</v>
+        <v>7308629</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2175,6 +2160,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2193,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117661399</v>
+        <v>117663055</v>
       </c>
       <c r="B15" t="n">
-        <v>78481</v>
+        <v>57288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2209,26 +2195,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2236,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>762825</v>
+        <v>763011</v>
       </c>
       <c r="R15" t="n">
-        <v>7308431</v>
+        <v>7308585</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2274,13 +2261,17 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2299,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117664449</v>
+        <v>117664474</v>
       </c>
       <c r="B16" t="n">
-        <v>90425</v>
+        <v>97872</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2311,25 +2302,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3242</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2330,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762801</v>
+        <v>762947</v>
       </c>
       <c r="R16" t="n">
-        <v>7308448</v>
+        <v>7308669</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2401,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117664476</v>
+        <v>117664469</v>
       </c>
       <c r="B17" t="n">
-        <v>97870</v>
+        <v>97756</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,21 +2408,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>223591</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2441,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>762925</v>
+        <v>762937</v>
       </c>
       <c r="R17" t="n">
-        <v>7308714</v>
+        <v>7308671</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2503,10 +2494,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117664474</v>
+        <v>117664475</v>
       </c>
       <c r="B18" t="n">
-        <v>97870</v>
+        <v>97872</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2543,10 +2534,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>762947</v>
+        <v>762938</v>
       </c>
       <c r="R18" t="n">
-        <v>7308669</v>
+        <v>7308665</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2605,10 +2596,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117663055</v>
+        <v>117664470</v>
       </c>
       <c r="B19" t="n">
-        <v>57287</v>
+        <v>97756</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,42 +2608,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>223591</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>763011</v>
+        <v>762765</v>
       </c>
       <c r="R19" t="n">
-        <v>7308585</v>
+        <v>7308648</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2687,39 +2674,35 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117664472</v>
+        <v>117661399</v>
       </c>
       <c r="B20" t="n">
-        <v>79465</v>
+        <v>78483</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2728,38 +2711,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>230405</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>762951</v>
+        <v>762825</v>
       </c>
       <c r="R20" t="n">
-        <v>7308667</v>
+        <v>7308431</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2800,28 +2786,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117664475</v>
+        <v>117664457</v>
       </c>
       <c r="B21" t="n">
-        <v>97870</v>
+        <v>56500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,34 +2821,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>762938</v>
+        <v>762798</v>
       </c>
       <c r="R21" t="n">
-        <v>7308665</v>
+        <v>7308440</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2896,6 +2887,11 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2913,17 +2909,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117664470</v>
+        <v>117663042</v>
       </c>
       <c r="B22" t="n">
-        <v>97754</v>
+        <v>90650</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2932,38 +2928,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223591</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>762765</v>
+        <v>762726</v>
       </c>
       <c r="R22" t="n">
-        <v>7308648</v>
+        <v>7308406</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3023,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117664471</v>
+        <v>117666782</v>
       </c>
       <c r="B23" t="n">
-        <v>97754</v>
+        <v>57170</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3035,38 +3034,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223591</v>
+        <v>100011</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>762933</v>
+        <v>762791</v>
       </c>
       <c r="R23" t="n">
-        <v>7308409</v>
+        <v>7308597</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3096,40 +3107,49 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117663042</v>
+        <v>117664467</v>
       </c>
       <c r="B24" t="n">
-        <v>90648</v>
+        <v>79592</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3138,41 +3158,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>762726</v>
+        <v>762934</v>
       </c>
       <c r="R24" t="n">
-        <v>7308406</v>
+        <v>7308414</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3213,7 +3230,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3232,10 +3248,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117664457</v>
+        <v>117664465</v>
       </c>
       <c r="B25" t="n">
-        <v>56499</v>
+        <v>79592</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3248,38 +3264,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>762798</v>
+        <v>762925</v>
       </c>
       <c r="R25" t="n">
-        <v>7308440</v>
+        <v>7308403</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3314,11 +3326,6 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3336,17 +3343,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117664477</v>
+        <v>117646899</v>
       </c>
       <c r="B26" t="n">
-        <v>97870</v>
+        <v>97838</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3355,38 +3362,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>762877</v>
+        <v>762982</v>
       </c>
       <c r="R26" t="n">
-        <v>7308488</v>
+        <v>7308684</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3427,28 +3446,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117667686</v>
+        <v>117646797</v>
       </c>
       <c r="B27" t="n">
-        <v>57303</v>
+        <v>97838</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3457,35 +3477,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3493,10 +3517,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>762976</v>
+        <v>763000</v>
       </c>
       <c r="R27" t="n">
-        <v>7308367</v>
+        <v>7308589</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3531,17 +3555,13 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3553,17 +3573,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117664473</v>
+        <v>117664477</v>
       </c>
       <c r="B28" t="n">
-        <v>97725</v>
+        <v>97872</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3572,25 +3592,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>233</v>
+        <v>219874</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3600,10 +3620,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>762931</v>
+        <v>762877</v>
       </c>
       <c r="R28" t="n">
-        <v>7308402</v>
+        <v>7308488</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3662,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117664467</v>
+        <v>117667686</v>
       </c>
       <c r="B29" t="n">
-        <v>79590</v>
+        <v>57304</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3674,38 +3694,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>762934</v>
+        <v>762976</v>
       </c>
       <c r="R29" t="n">
-        <v>7308414</v>
+        <v>7308367</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3740,6 +3768,11 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3752,22 +3785,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117646899</v>
+        <v>117664476</v>
       </c>
       <c r="B30" t="n">
-        <v>97836</v>
+        <v>97872</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3776,50 +3809,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>762982</v>
+        <v>762925</v>
       </c>
       <c r="R30" t="n">
-        <v>7308684</v>
+        <v>7308714</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3860,29 +3881,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117646797</v>
+        <v>117664472</v>
       </c>
       <c r="B31" t="n">
-        <v>97836</v>
+        <v>79467</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3891,50 +3911,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>763000</v>
+        <v>762951</v>
       </c>
       <c r="R31" t="n">
-        <v>7308589</v>
+        <v>7308667</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3975,29 +3983,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117645796</v>
+        <v>117664471</v>
       </c>
       <c r="B32" t="n">
-        <v>97836</v>
+        <v>97756</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4006,50 +4013,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>762953</v>
+        <v>762933</v>
       </c>
       <c r="R32" t="n">
-        <v>7308667</v>
+        <v>7308409</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4097,22 +4092,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117659873</v>
+        <v>117659961</v>
       </c>
       <c r="B33" t="n">
-        <v>78216</v>
+        <v>78219</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4125,21 +4120,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4156,10 +4151,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>762765</v>
+        <v>762953</v>
       </c>
       <c r="R33" t="n">
-        <v>7308409</v>
+        <v>7308413</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4219,10 +4214,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117661434</v>
+        <v>117664473</v>
       </c>
       <c r="B34" t="n">
-        <v>82259</v>
+        <v>97727</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4231,45 +4226,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>233</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>762980</v>
+        <v>762931</v>
       </c>
       <c r="R34" t="n">
-        <v>7308629</v>
+        <v>7308402</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4310,7 +4298,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4329,10 +4316,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117664465</v>
+        <v>117659873</v>
       </c>
       <c r="B35" t="n">
-        <v>79590</v>
+        <v>78218</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4341,38 +4328,45 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>762925</v>
+        <v>762765</v>
       </c>
       <c r="R35" t="n">
-        <v>7308403</v>
+        <v>7308409</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4413,6 +4407,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4431,10 +4426,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117659961</v>
+        <v>117645796</v>
       </c>
       <c r="B36" t="n">
-        <v>78217</v>
+        <v>97838</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4443,34 +4438,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>762953</v>
       </c>
       <c r="R36" t="n">
-        <v>7308413</v>
+        <v>7308667</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4529,22 +4529,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117664469</v>
+        <v>117664464</v>
       </c>
       <c r="B37" t="n">
-        <v>97754</v>
+        <v>79592</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223591</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>762937</v>
+        <v>762992</v>
       </c>
       <c r="R37" t="n">
-        <v>7308671</v>
+        <v>7308570</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4643,10 +4643,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117996065</v>
+        <v>117996046</v>
       </c>
       <c r="B38" t="n">
-        <v>97836</v>
+        <v>97756</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4655,25 +4655,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4683,10 +4683,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>762908</v>
+        <v>762949</v>
       </c>
       <c r="R38" t="n">
-        <v>7308658</v>
+        <v>7308733</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4727,6 +4727,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4745,10 +4746,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117996057</v>
+        <v>117995646</v>
       </c>
       <c r="B39" t="n">
-        <v>97836</v>
+        <v>97755</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4757,38 +4758,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>763015</v>
+        <v>762898</v>
       </c>
       <c r="R39" t="n">
-        <v>7308599</v>
+        <v>7308634</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4829,29 +4830,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117995631</v>
+        <v>117996064</v>
       </c>
       <c r="B40" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4884,14 +4884,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>762898</v>
+        <v>762909</v>
       </c>
       <c r="R40" t="n">
-        <v>7308634</v>
+        <v>7308662</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4938,22 +4938,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117995634</v>
+        <v>117996037</v>
       </c>
       <c r="B41" t="n">
-        <v>97836</v>
+        <v>79592</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4962,38 +4962,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>762899</v>
+        <v>762933</v>
       </c>
       <c r="R41" t="n">
-        <v>7308644</v>
+        <v>7308827</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5040,22 +5040,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117996037</v>
+        <v>117996057</v>
       </c>
       <c r="B42" t="n">
-        <v>79590</v>
+        <v>97838</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5064,25 +5064,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>762933</v>
+        <v>763015</v>
       </c>
       <c r="R42" t="n">
-        <v>7308827</v>
+        <v>7308599</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5136,6 +5136,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5154,10 +5155,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117995633</v>
+        <v>117996070</v>
       </c>
       <c r="B43" t="n">
-        <v>97836</v>
+        <v>97756</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5166,38 +5167,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>762884</v>
+        <v>762942</v>
       </c>
       <c r="R43" t="n">
-        <v>7308624</v>
+        <v>7308749</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5238,28 +5239,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117996052</v>
+        <v>117996049</v>
       </c>
       <c r="B44" t="n">
-        <v>97870</v>
+        <v>97840</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5272,21 +5274,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>219811</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5296,10 +5298,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>762974</v>
+        <v>762954</v>
       </c>
       <c r="R44" t="n">
-        <v>7308742</v>
+        <v>7308830</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5358,10 +5360,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117996070</v>
+        <v>117995608</v>
       </c>
       <c r="B45" t="n">
-        <v>97754</v>
+        <v>97872</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5374,34 +5376,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>223591</v>
+        <v>219874</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>762942</v>
+        <v>762928</v>
       </c>
       <c r="R45" t="n">
-        <v>7308749</v>
+        <v>7308793</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5442,29 +5444,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117996043</v>
+        <v>117996065</v>
       </c>
       <c r="B46" t="n">
-        <v>57303</v>
+        <v>97838</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5473,25 +5474,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5501,10 +5502,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>762976</v>
+        <v>762908</v>
       </c>
       <c r="R46" t="n">
-        <v>7308712</v>
+        <v>7308658</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5563,10 +5564,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117995606</v>
+        <v>117996041</v>
       </c>
       <c r="B47" t="n">
-        <v>97870</v>
+        <v>97859</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5579,16 +5580,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5599,14 +5600,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>762892</v>
+        <v>762896</v>
       </c>
       <c r="R47" t="n">
-        <v>7308626</v>
+        <v>7308661</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5653,22 +5654,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117996049</v>
+        <v>117996036</v>
       </c>
       <c r="B48" t="n">
-        <v>97838</v>
+        <v>90501</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5677,25 +5678,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219811</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5706,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>762954</v>
+        <v>762963</v>
       </c>
       <c r="R48" t="n">
-        <v>7308830</v>
+        <v>7308745</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5770,7 +5771,7 @@
         <v>117995630</v>
       </c>
       <c r="B49" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5869,10 +5870,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117995608</v>
+        <v>117995634</v>
       </c>
       <c r="B50" t="n">
-        <v>97870</v>
+        <v>97838</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5881,25 +5882,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5909,10 +5910,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>762928</v>
+        <v>762899</v>
       </c>
       <c r="R50" t="n">
-        <v>7308793</v>
+        <v>7308644</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -5971,10 +5972,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117995635</v>
+        <v>117996047</v>
       </c>
       <c r="B51" t="n">
-        <v>97836</v>
+        <v>97756</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5983,38 +5984,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>762962</v>
+        <v>762937</v>
       </c>
       <c r="R51" t="n">
-        <v>7308672</v>
+        <v>7308759</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6055,28 +6056,29 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117996047</v>
+        <v>117996055</v>
       </c>
       <c r="B52" t="n">
-        <v>97754</v>
+        <v>79599</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6089,21 +6091,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223591</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6113,10 +6115,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>762937</v>
+        <v>762931</v>
       </c>
       <c r="R52" t="n">
-        <v>7308759</v>
+        <v>7308827</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6157,7 +6159,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6176,10 +6177,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117995646</v>
+        <v>117996063</v>
       </c>
       <c r="B53" t="n">
-        <v>97753</v>
+        <v>97838</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6188,38 +6189,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>762898</v>
+        <v>762979</v>
       </c>
       <c r="R53" t="n">
-        <v>7308634</v>
+        <v>7308612</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6266,22 +6267,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117996041</v>
+        <v>117995635</v>
       </c>
       <c r="B54" t="n">
-        <v>97857</v>
+        <v>97838</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6290,38 +6291,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>762896</v>
+        <v>762962</v>
       </c>
       <c r="R54" t="n">
-        <v>7308661</v>
+        <v>7308672</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6368,22 +6369,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117995607</v>
+        <v>117995604</v>
       </c>
       <c r="B55" t="n">
-        <v>97870</v>
+        <v>97872</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6420,10 +6421,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>762982</v>
+        <v>762955</v>
       </c>
       <c r="R55" t="n">
-        <v>7308743</v>
+        <v>7308825</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6482,10 +6483,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117996036</v>
+        <v>117995633</v>
       </c>
       <c r="B56" t="n">
-        <v>90499</v>
+        <v>97838</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6494,38 +6495,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>762963</v>
+        <v>762884</v>
       </c>
       <c r="R56" t="n">
-        <v>7308745</v>
+        <v>7308624</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -6572,22 +6573,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117996046</v>
+        <v>117996068</v>
       </c>
       <c r="B57" t="n">
-        <v>97754</v>
+        <v>56492</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6596,25 +6597,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>223591</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6624,10 +6625,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>762949</v>
+        <v>762952</v>
       </c>
       <c r="R57" t="n">
-        <v>7308733</v>
+        <v>7308740</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6668,7 +6669,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6687,10 +6687,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117996063</v>
+        <v>117996040</v>
       </c>
       <c r="B58" t="n">
-        <v>97836</v>
+        <v>97859</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6699,25 +6699,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>762979</v>
+        <v>762910</v>
       </c>
       <c r="R58" t="n">
-        <v>7308612</v>
+        <v>7308657</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6789,10 +6789,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117996055</v>
+        <v>117996053</v>
       </c>
       <c r="B59" t="n">
-        <v>79597</v>
+        <v>97872</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6805,21 +6805,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6464</v>
+        <v>219874</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>762931</v>
+        <v>762933</v>
       </c>
       <c r="R59" t="n">
-        <v>7308827</v>
+        <v>7308841</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117996068</v>
+        <v>117996043</v>
       </c>
       <c r="B60" t="n">
-        <v>56491</v>
+        <v>57304</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6907,16 +6907,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>762952</v>
+        <v>762976</v>
       </c>
       <c r="R60" t="n">
-        <v>7308740</v>
+        <v>7308712</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -6993,10 +6993,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117995604</v>
+        <v>117995606</v>
       </c>
       <c r="B61" t="n">
-        <v>97870</v>
+        <v>97872</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>762955</v>
+        <v>762892</v>
       </c>
       <c r="R61" t="n">
-        <v>7308825</v>
+        <v>7308626</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7095,10 +7095,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117996064</v>
+        <v>117996052</v>
       </c>
       <c r="B62" t="n">
-        <v>97836</v>
+        <v>97872</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7107,25 +7107,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>762909</v>
+        <v>762974</v>
       </c>
       <c r="R62" t="n">
-        <v>7308662</v>
+        <v>7308742</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7197,10 +7197,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117996040</v>
+        <v>117995631</v>
       </c>
       <c r="B63" t="n">
-        <v>97857</v>
+        <v>97838</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7209,38 +7209,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>762910</v>
+        <v>762898</v>
       </c>
       <c r="R63" t="n">
-        <v>7308657</v>
+        <v>7308634</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7287,22 +7287,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117996053</v>
+        <v>117995607</v>
       </c>
       <c r="B64" t="n">
-        <v>97870</v>
+        <v>97872</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7335,14 +7335,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>762933</v>
+        <v>762982</v>
       </c>
       <c r="R64" t="n">
-        <v>7308841</v>
+        <v>7308743</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7389,12 +7389,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>

--- a/artfynd/A 16092-2024 artfynd.xlsx
+++ b/artfynd/A 16092-2024 artfynd.xlsx
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117661399</v>
+        <v>117664457</v>
       </c>
       <c r="B20" t="n">
-        <v>78483</v>
+        <v>56500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,30 +2711,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>230405</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2742,10 +2743,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>762825</v>
+        <v>762798</v>
       </c>
       <c r="R20" t="n">
-        <v>7308431</v>
+        <v>7308440</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2780,35 +2781,39 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117664457</v>
+        <v>117661399</v>
       </c>
       <c r="B21" t="n">
-        <v>56500</v>
+        <v>78483</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2817,31 +2822,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>230405</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2849,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>762798</v>
+        <v>762825</v>
       </c>
       <c r="R21" t="n">
-        <v>7308440</v>
+        <v>7308431</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2887,29 +2891,25 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117664473</v>
+        <v>117645796</v>
       </c>
       <c r="B34" t="n">
-        <v>97727</v>
+        <v>97838</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4230,34 +4230,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>233</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>762931</v>
+        <v>762953</v>
       </c>
       <c r="R34" t="n">
-        <v>7308402</v>
+        <v>7308667</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4298,28 +4310,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117659873</v>
+        <v>117664473</v>
       </c>
       <c r="B35" t="n">
-        <v>78218</v>
+        <v>97727</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4328,45 +4341,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>233</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>762765</v>
+        <v>762931</v>
       </c>
       <c r="R35" t="n">
-        <v>7308409</v>
+        <v>7308402</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4407,7 +4413,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4426,10 +4431,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117645796</v>
+        <v>117659873</v>
       </c>
       <c r="B36" t="n">
-        <v>97838</v>
+        <v>78218</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4438,39 +4443,34 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>762953</v>
+        <v>762765</v>
       </c>
       <c r="R36" t="n">
-        <v>7308667</v>
+        <v>7308409</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4529,12 +4529,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117996046</v>
+        <v>117995646</v>
       </c>
       <c r="B38" t="n">
-        <v>97756</v>
+        <v>97755</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>762949</v>
+        <v>762898</v>
       </c>
       <c r="R38" t="n">
-        <v>7308733</v>
+        <v>7308634</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4727,29 +4727,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117995646</v>
+        <v>117996064</v>
       </c>
       <c r="B39" t="n">
-        <v>97755</v>
+        <v>97838</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4758,38 +4757,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>762898</v>
+        <v>762909</v>
       </c>
       <c r="R39" t="n">
-        <v>7308634</v>
+        <v>7308662</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4836,22 +4835,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117996064</v>
+        <v>117996046</v>
       </c>
       <c r="B40" t="n">
-        <v>97838</v>
+        <v>97756</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4860,25 +4859,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4888,10 +4887,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>762909</v>
+        <v>762949</v>
       </c>
       <c r="R40" t="n">
-        <v>7308662</v>
+        <v>7308733</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4932,6 +4931,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5666,10 +5666,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117996036</v>
+        <v>117995630</v>
       </c>
       <c r="B48" t="n">
-        <v>90501</v>
+        <v>97838</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5678,38 +5678,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>762963</v>
+        <v>763021</v>
       </c>
       <c r="R48" t="n">
-        <v>7308745</v>
+        <v>7308620</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5756,22 +5756,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117995630</v>
+        <v>117996036</v>
       </c>
       <c r="B49" t="n">
-        <v>97838</v>
+        <v>90501</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5780,38 +5780,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>763021</v>
+        <v>762963</v>
       </c>
       <c r="R49" t="n">
-        <v>7308620</v>
+        <v>7308745</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -5858,12 +5858,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6483,10 +6483,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117995633</v>
+        <v>117996068</v>
       </c>
       <c r="B56" t="n">
-        <v>97838</v>
+        <v>56492</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6495,38 +6495,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>762884</v>
+        <v>762952</v>
       </c>
       <c r="R56" t="n">
-        <v>7308624</v>
+        <v>7308740</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -6573,22 +6573,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117996068</v>
+        <v>117995633</v>
       </c>
       <c r="B57" t="n">
-        <v>56492</v>
+        <v>97838</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6597,38 +6597,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>762952</v>
+        <v>762884</v>
       </c>
       <c r="R57" t="n">
-        <v>7308740</v>
+        <v>7308624</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6675,12 +6675,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>

--- a/artfynd/A 16092-2024 artfynd.xlsx
+++ b/artfynd/A 16092-2024 artfynd.xlsx
@@ -3450,11 +3450,11 @@
         <v>117666782</v>
       </c>
       <c r="B27" t="n">
-        <v>57170</v>
+        <v>57264</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">

--- a/artfynd/A 16092-2024 artfynd.xlsx
+++ b/artfynd/A 16092-2024 artfynd.xlsx
@@ -3450,7 +3450,7 @@
         <v>117666782</v>
       </c>
       <c r="B27" t="n">
-        <v>57358</v>
+        <v>57361</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 16092-2024 artfynd.xlsx
+++ b/artfynd/A 16092-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79384551</v>
+        <v>118163552</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763065.9856044251</v>
+        <v>762933</v>
       </c>
       <c r="R2" t="n">
-        <v>7308363.914566147</v>
+        <v>7308639</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,80 +761,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Gårdman, Liam Martin</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79384552</v>
+        <v>117664473</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>233</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Oakes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763065.9856044251</v>
+        <v>762931</v>
       </c>
       <c r="R3" t="n">
-        <v>7308363.914566147</v>
+        <v>7308402</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,74 +865,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Gårdman, Liam Martin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79384550</v>
+        <v>117996036</v>
       </c>
       <c r="B4" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>763065.9856044251</v>
+        <v>762963</v>
       </c>
       <c r="R4" t="n">
-        <v>7308363.914566147</v>
+        <v>7308745</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,27 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>21 överblommade ex. och 12 ex. med endast blad.</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,69 +962,67 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Gårdman, Liam Martin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79384415</v>
+        <v>117661434</v>
       </c>
       <c r="B5" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>763092.2449463888</v>
+        <v>762980</v>
       </c>
       <c r="R5" t="n">
-        <v>7308365.91564002</v>
+        <v>7308629</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,69 +1067,63 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Gårdman, Liam Martin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79384609</v>
+        <v>117663042</v>
       </c>
       <c r="B6" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763090.4220964119</v>
+        <v>762726</v>
       </c>
       <c r="R6" t="n">
-        <v>7308363.271821027</v>
+        <v>7308406</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,27 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Gårdman, Liam Martin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117646766</v>
+        <v>118156998</v>
       </c>
       <c r="B7" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,35 +1191,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1329,13 +1222,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762890</v>
+        <v>762957</v>
       </c>
       <c r="R7" t="n">
-        <v>7308462</v>
+        <v>7308729</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,12 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,74 +1273,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117646738</v>
+        <v>117664449</v>
       </c>
       <c r="B8" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762979</v>
+        <v>762801</v>
       </c>
       <c r="R8" t="n">
-        <v>7308557</v>
+        <v>7308448</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1488,81 +1364,63 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117646870</v>
+        <v>117664462</v>
       </c>
       <c r="B9" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762973</v>
+        <v>762702</v>
       </c>
       <c r="R9" t="n">
-        <v>7308555</v>
+        <v>7308444</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1603,70 +1461,55 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117646835</v>
+        <v>118163408</v>
       </c>
       <c r="B10" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1674,13 +1517,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762967</v>
+        <v>762897</v>
       </c>
       <c r="R10" t="n">
-        <v>7308415</v>
+        <v>7308640</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,12 +1547,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,63 +1568,53 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117646676</v>
+        <v>117659873</v>
       </c>
       <c r="B11" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1789,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762976</v>
+        <v>762765</v>
       </c>
       <c r="R11" t="n">
-        <v>7308680</v>
+        <v>7308409</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1840,74 +1673,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117646699</v>
+        <v>117664472</v>
       </c>
       <c r="B12" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762936</v>
+        <v>762951</v>
       </c>
       <c r="R12" t="n">
-        <v>7308406</v>
+        <v>7308667</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1948,76 +1764,63 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117661434</v>
+        <v>117664464</v>
       </c>
       <c r="B13" t="n">
-        <v>82261</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762980</v>
+        <v>762992</v>
       </c>
       <c r="R13" t="n">
-        <v>7308629</v>
+        <v>7308570</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2058,7 +1861,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2077,15 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117664467</v>
+        <v>117664465</v>
       </c>
       <c r="B14" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>762934</v>
+        <v>762925</v>
       </c>
       <c r="R14" t="n">
-        <v>7308414</v>
+        <v>7308403</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2179,62 +1976,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117645796</v>
+        <v>117664467</v>
       </c>
       <c r="B15" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>762953</v>
+        <v>762934</v>
       </c>
       <c r="R15" t="n">
-        <v>7308667</v>
+        <v>7308414</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2275,69 +2055,63 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117664473</v>
+        <v>117996037</v>
       </c>
       <c r="B16" t="n">
-        <v>97727</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>233</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762931</v>
+        <v>762933</v>
       </c>
       <c r="R16" t="n">
-        <v>7308402</v>
+        <v>7308827</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2364,12 +2138,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,15 +2170,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117664474</v>
+        <v>118163431</v>
       </c>
       <c r="B17" t="n">
-        <v>97872</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,37 +2181,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>762947</v>
+        <v>762898</v>
       </c>
       <c r="R17" t="n">
-        <v>7308669</v>
+        <v>7308632</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2466,12 +2238,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,33 +2252,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117664476</v>
+        <v>117996055</v>
       </c>
       <c r="B18" t="n">
-        <v>97872</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,34 +2282,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>762925</v>
+        <v>762931</v>
       </c>
       <c r="R18" t="n">
-        <v>7308714</v>
+        <v>7308827</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2568,12 +2336,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,50 +2368,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117664475</v>
+        <v>117666782</v>
       </c>
       <c r="B19" t="n">
-        <v>97872</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>100011</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>762938</v>
+        <v>762791</v>
       </c>
       <c r="R19" t="n">
-        <v>7308665</v>
+        <v>7308597</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2673,9 +2448,19 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,27 +2475,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117664457</v>
+        <v>117667686</v>
       </c>
       <c r="B20" t="n">
-        <v>56500</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,27 +2498,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2746,10 +2530,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>762798</v>
+        <v>762976</v>
       </c>
       <c r="R20" t="n">
-        <v>7308440</v>
+        <v>7308367</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2786,7 +2570,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,69 +2585,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117659873</v>
+        <v>117996043</v>
       </c>
       <c r="B21" t="n">
-        <v>78218</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>762765</v>
+        <v>762976</v>
       </c>
       <c r="R21" t="n">
-        <v>7308409</v>
+        <v>7308712</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2890,12 +2662,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2904,7 +2676,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2923,50 +2694,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117664471</v>
+        <v>117663055</v>
       </c>
       <c r="B22" t="n">
-        <v>97756</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223591</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>762933</v>
+        <v>763011</v>
       </c>
       <c r="R22" t="n">
-        <v>7308409</v>
+        <v>7308585</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3001,40 +2771,39 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117664464</v>
+        <v>117996068</v>
       </c>
       <c r="B23" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3042,34 +2811,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>762992</v>
+        <v>762952</v>
       </c>
       <c r="R23" t="n">
-        <v>7308570</v>
+        <v>7308740</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3096,12 +2865,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,15 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117664477</v>
+        <v>79384552</v>
       </c>
       <c r="B24" t="n">
-        <v>97872</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,37 +2908,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>762877</v>
+        <v>763066</v>
       </c>
       <c r="R24" t="n">
-        <v>7308488</v>
+        <v>7308364</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3198,12 +2971,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,27 +2991,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117664469</v>
+        <v>117995646</v>
       </c>
       <c r="B25" t="n">
-        <v>97756</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,21 +3014,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3038,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>762937</v>
+        <v>762898</v>
       </c>
       <c r="R25" t="n">
-        <v>7308671</v>
+        <v>7308634</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3300,12 +3068,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3320,74 +3088,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117646797</v>
+        <v>117995647</v>
       </c>
       <c r="B26" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>763000</v>
+        <v>762997</v>
       </c>
       <c r="R26" t="n">
-        <v>7308589</v>
+        <v>7308807</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3414,12 +3165,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3428,7 +3179,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3447,62 +3197,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117666782</v>
+        <v>117996049</v>
       </c>
       <c r="B27" t="n">
-        <v>57361</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100011</v>
+        <v>219811</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>762791</v>
+        <v>762954</v>
       </c>
       <c r="R27" t="n">
-        <v>7308597</v>
+        <v>7308830</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3529,22 +3262,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,27 +3282,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117664470</v>
+        <v>79384550</v>
       </c>
       <c r="B28" t="n">
-        <v>97756</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,37 +3305,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223591</v>
+        <v>219874</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>762765</v>
+        <v>763066</v>
       </c>
       <c r="R28" t="n">
-        <v>7308648</v>
+        <v>7308364</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3641,12 +3368,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2019-08-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>21 överblommade ex. och 12 ex. med endast blad.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3655,81 +3387,63 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117646899</v>
+        <v>117664474</v>
       </c>
       <c r="B29" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>762982</v>
+        <v>762947</v>
       </c>
       <c r="R29" t="n">
-        <v>7308684</v>
+        <v>7308669</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3770,77 +3484,63 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117667686</v>
+        <v>117664475</v>
       </c>
       <c r="B30" t="n">
-        <v>57304</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>762976</v>
+        <v>762938</v>
       </c>
       <c r="R30" t="n">
-        <v>7308367</v>
+        <v>7308665</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3875,11 +3575,6 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3892,27 +3587,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117664472</v>
+        <v>117664476</v>
       </c>
       <c r="B31" t="n">
-        <v>79467</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3920,21 +3610,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>219874</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3944,10 +3634,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>762951</v>
+        <v>762925</v>
       </c>
       <c r="R31" t="n">
-        <v>7308667</v>
+        <v>7308714</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4006,54 +3696,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117663055</v>
+        <v>117664477</v>
       </c>
       <c r="B32" t="n">
-        <v>57288</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>763011</v>
+        <v>762877</v>
       </c>
       <c r="R32" t="n">
-        <v>7308585</v>
+        <v>7308488</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4088,11 +3769,6 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4105,65 +3781,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117661399</v>
+        <v>117995604</v>
       </c>
       <c r="B33" t="n">
-        <v>78483</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230405</v>
+        <v>219874</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>762825</v>
+        <v>762955</v>
       </c>
       <c r="R33" t="n">
-        <v>7308431</v>
+        <v>7308825</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4190,12 +3858,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4204,7 +3872,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4216,44 +3883,39 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117664449</v>
+        <v>117995606</v>
       </c>
       <c r="B34" t="n">
-        <v>90427</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3242</v>
+        <v>219874</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4263,10 +3925,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>762801</v>
+        <v>762892</v>
       </c>
       <c r="R34" t="n">
-        <v>7308448</v>
+        <v>7308626</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4293,12 +3955,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4313,65 +3975,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117663042</v>
+        <v>117995607</v>
       </c>
       <c r="B35" t="n">
-        <v>90650</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1503</v>
+        <v>219874</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>762726</v>
+        <v>762982</v>
       </c>
       <c r="R35" t="n">
-        <v>7308406</v>
+        <v>7308743</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4398,12 +4052,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4412,76 +4066,63 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117659961</v>
+        <v>117995608</v>
       </c>
       <c r="B36" t="n">
-        <v>78219</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>219874</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>762953</v>
+        <v>762928</v>
       </c>
       <c r="R36" t="n">
-        <v>7308413</v>
+        <v>7308793</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4508,12 +4149,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4522,34 +4163,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117664465</v>
+        <v>117995609</v>
       </c>
       <c r="B37" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,21 +4192,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4216,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>762925</v>
+        <v>762979</v>
       </c>
       <c r="R37" t="n">
-        <v>7308403</v>
+        <v>7308812</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4611,12 +4246,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4631,27 +4266,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117996070</v>
+        <v>117996052</v>
       </c>
       <c r="B38" t="n">
-        <v>97764</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4659,21 +4289,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>223591</v>
+        <v>219874</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4683,10 +4313,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>762942</v>
+        <v>762974</v>
       </c>
       <c r="R38" t="n">
-        <v>7308749</v>
+        <v>7308742</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4727,7 +4357,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4746,15 +4375,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117995607</v>
+        <v>117996053</v>
       </c>
       <c r="B39" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4782,14 +4406,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>762982</v>
+        <v>762933</v>
       </c>
       <c r="R39" t="n">
-        <v>7308743</v>
+        <v>7308841</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4836,27 +4460,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117995606</v>
+        <v>118156874</v>
       </c>
       <c r="B40" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4882,19 +4501,27 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>762892</v>
+        <v>762977</v>
       </c>
       <c r="R40" t="n">
-        <v>7308626</v>
+        <v>7308824</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4932,71 +4559,75 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117996064</v>
+        <v>118156936</v>
       </c>
       <c r="B41" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>762909</v>
+        <v>762984</v>
       </c>
       <c r="R41" t="n">
-        <v>7308662</v>
+        <v>7308842</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5034,71 +4665,75 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117995630</v>
+        <v>118156952</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>763021</v>
+        <v>762967</v>
       </c>
       <c r="R42" t="n">
-        <v>7308620</v>
+        <v>7308839</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5136,33 +4771,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117996049</v>
+        <v>118156977</v>
       </c>
       <c r="B43" t="n">
-        <v>97848</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5170,37 +4801,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219811</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>762954</v>
+        <v>762953</v>
       </c>
       <c r="R43" t="n">
-        <v>7308830</v>
+        <v>7308823</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5238,33 +4877,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117996040</v>
+        <v>118163444</v>
       </c>
       <c r="B44" t="n">
-        <v>97867</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,16 +4907,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5290,19 +4925,27 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>762910</v>
+        <v>762905</v>
       </c>
       <c r="R44" t="n">
-        <v>7308657</v>
+        <v>7308628</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5340,33 +4983,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117996037</v>
+        <v>118163531</v>
       </c>
       <c r="B45" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5374,37 +5013,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>762933</v>
+        <v>762869</v>
       </c>
       <c r="R45" t="n">
-        <v>7308827</v>
+        <v>7308618</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5442,71 +5089,75 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117996063</v>
+        <v>118163588</v>
       </c>
       <c r="B46" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>762979</v>
+        <v>763067</v>
       </c>
       <c r="R46" t="n">
-        <v>7308612</v>
+        <v>7308681</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5544,33 +5195,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117995634</v>
+        <v>79384551</v>
       </c>
       <c r="B47" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5595,20 +5242,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>762899</v>
+        <v>763066</v>
       </c>
       <c r="R47" t="n">
-        <v>7308644</v>
+        <v>7308364</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5632,12 +5288,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5652,62 +5308,69 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117996043</v>
+        <v>117645796</v>
       </c>
       <c r="B48" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>762976</v>
+        <v>762953</v>
       </c>
       <c r="R48" t="n">
-        <v>7308712</v>
+        <v>7308667</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5734,12 +5397,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5748,68 +5411,76 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117996068</v>
+        <v>117646676</v>
       </c>
       <c r="B49" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>762952</v>
+        <v>762976</v>
       </c>
       <c r="R49" t="n">
-        <v>7308740</v>
+        <v>7308680</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -5836,12 +5507,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5850,68 +5521,76 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117996046</v>
+        <v>117646699</v>
       </c>
       <c r="B50" t="n">
-        <v>97764</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>762949</v>
+        <v>762936</v>
       </c>
       <c r="R50" t="n">
-        <v>7308733</v>
+        <v>7308406</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -5938,12 +5617,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5959,27 +5638,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117995631</v>
+        <v>117646738</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6004,17 +5678,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>762898</v>
+        <v>762979</v>
       </c>
       <c r="R51" t="n">
-        <v>7308634</v>
+        <v>7308557</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6041,12 +5727,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6055,6 +5741,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6073,50 +5760,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117995646</v>
+        <v>117646766</v>
       </c>
       <c r="B52" t="n">
-        <v>97763</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>762898</v>
+        <v>762890</v>
       </c>
       <c r="R52" t="n">
-        <v>7308634</v>
+        <v>7308462</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6143,12 +5837,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6157,6 +5851,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6175,50 +5870,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117995608</v>
+        <v>117646797</v>
       </c>
       <c r="B53" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>762928</v>
+        <v>763000</v>
       </c>
       <c r="R53" t="n">
-        <v>7308793</v>
+        <v>7308589</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6245,12 +5947,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6259,6 +5961,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6277,50 +5980,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117996041</v>
+        <v>117646835</v>
       </c>
       <c r="B54" t="n">
-        <v>97867</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>762896</v>
+        <v>762967</v>
       </c>
       <c r="R54" t="n">
-        <v>7308661</v>
+        <v>7308415</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6347,12 +6057,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6361,68 +6071,76 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117996036</v>
+        <v>117646870</v>
       </c>
       <c r="B55" t="n">
-        <v>90504</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>762963</v>
+        <v>762973</v>
       </c>
       <c r="R55" t="n">
-        <v>7308745</v>
+        <v>7308555</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6449,12 +6167,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6463,33 +6181,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117995635</v>
+        <v>117646899</v>
       </c>
       <c r="B56" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,17 +6228,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>762962</v>
+        <v>762982</v>
       </c>
       <c r="R56" t="n">
-        <v>7308672</v>
+        <v>7308684</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -6551,12 +6277,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6565,6 +6291,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6576,44 +6303,39 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117995604</v>
+        <v>117995630</v>
       </c>
       <c r="B57" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6623,10 +6345,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>762955</v>
+        <v>763021</v>
       </c>
       <c r="R57" t="n">
-        <v>7308825</v>
+        <v>7308620</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6685,15 +6407,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117995633</v>
+        <v>117995631</v>
       </c>
       <c r="B58" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6725,10 +6442,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>762884</v>
+        <v>762898</v>
       </c>
       <c r="R58" t="n">
-        <v>7308624</v>
+        <v>7308634</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6787,50 +6504,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117996053</v>
+        <v>117995633</v>
       </c>
       <c r="B59" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>762933</v>
+        <v>762884</v>
       </c>
       <c r="R59" t="n">
-        <v>7308841</v>
+        <v>7308624</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6877,62 +6589,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117996052</v>
+        <v>117995634</v>
       </c>
       <c r="B60" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>762974</v>
+        <v>762899</v>
       </c>
       <c r="R60" t="n">
-        <v>7308742</v>
+        <v>7308644</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -6979,27 +6686,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117996065</v>
+        <v>117995635</v>
       </c>
       <c r="B61" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7027,14 +6729,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>762908</v>
+        <v>762962</v>
       </c>
       <c r="R61" t="n">
-        <v>7308658</v>
+        <v>7308672</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7081,62 +6783,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117996047</v>
+        <v>117995636</v>
       </c>
       <c r="B62" t="n">
-        <v>97764</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>762937</v>
+        <v>762993</v>
       </c>
       <c r="R62" t="n">
-        <v>7308759</v>
+        <v>7308807</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7177,19 +6874,18 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7199,12 +6895,7 @@
         <v>117996057</v>
       </c>
       <c r="B63" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7299,37 +6990,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117996055</v>
+        <v>117996063</v>
       </c>
       <c r="B64" t="n">
-        <v>79601</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7339,10 +7025,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>762931</v>
+        <v>762979</v>
       </c>
       <c r="R64" t="n">
-        <v>7308827</v>
+        <v>7308612</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7401,15 +7087,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118163552</v>
+        <v>117996064</v>
       </c>
       <c r="B65" t="n">
-        <v>90749</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7417,44 +7098,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>65</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>762933</v>
+        <v>762909</v>
       </c>
       <c r="R65" t="n">
-        <v>7308639</v>
+        <v>7308662</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7492,80 +7166,66 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118163531</v>
+        <v>117996065</v>
       </c>
       <c r="B66" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>762869</v>
+        <v>762908</v>
       </c>
       <c r="R66" t="n">
-        <v>7308618</v>
+        <v>7308658</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7603,34 +7263,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118163408</v>
+        <v>117662650</v>
       </c>
       <c r="B67" t="n">
-        <v>74580</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7638,26 +7292,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6439</v>
+        <v>221725</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7665,13 +7324,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>762897</v>
+        <v>763069</v>
       </c>
       <c r="R67" t="n">
-        <v>7308640</v>
+        <v>7308635</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7695,12 +7354,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7716,27 +7375,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118163431</v>
+        <v>79384381</v>
       </c>
       <c r="B68" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7744,40 +7398,41 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>762898</v>
+        <v>763046</v>
       </c>
       <c r="R68" t="n">
-        <v>7308632</v>
+        <v>7308309</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7801,12 +7456,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7822,72 +7477,64 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118156998</v>
+        <v>79384415</v>
       </c>
       <c r="B69" t="n">
-        <v>90654</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>762957</v>
+        <v>763092</v>
       </c>
       <c r="R69" t="n">
-        <v>7308729</v>
+        <v>7308366</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7911,12 +7558,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7932,27 +7579,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118156977</v>
+        <v>79384609</v>
       </c>
       <c r="B70" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7960,45 +7602,41 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219874</v>
+        <v>221941</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällforsbergets SO sluttning, Övre Tväråsel, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>762953</v>
+        <v>763090</v>
       </c>
       <c r="R70" t="n">
-        <v>7308823</v>
+        <v>7308363</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8022,12 +7660,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8043,27 +7681,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Gårdman, Liam Martin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118163444</v>
+        <v>117996040</v>
       </c>
       <c r="B71" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8071,16 +7704,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8089,27 +7722,19 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>762905</v>
+        <v>762910</v>
       </c>
       <c r="R71" t="n">
-        <v>7308628</v>
+        <v>7308657</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8147,22 +7772,1218 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>117996041</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Fällfors, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>762896</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7308661</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>117996042</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Fällfors, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>762982</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7308804</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>117664469</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>762937</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7308671</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>117664470</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>762765</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7308648</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>117664471</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>762933</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7308409</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>117996046</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Fällfors, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>762949</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7308733</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>117996047</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Fällfors, Nb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>762937</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7308759</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>117996070</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Fällfors, Nb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>762942</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7308749</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>117659961</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>762953</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7308413</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>117660195</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>762948</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7308363</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>117660300</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>762720</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7308402</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>117661399</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>762825</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7308431</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16092-2024 artfynd.xlsx
+++ b/artfynd/A 16092-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AZ83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118163552</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664473</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996036</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117661434</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117663042</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118156998</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664449</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664462</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118163408</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117659873</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664472</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664464</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664465</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664467</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2167,6 +2242,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996037</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2268,6 +2348,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118163431</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2365,6 +2450,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996055</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2484,6 +2574,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117666782</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2594,6 +2689,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117667686</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2691,6 +2791,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996043</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2797,6 +2902,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117663055</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996068</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3000,6 +3115,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384552</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3097,6 +3217,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995646</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3194,6 +3319,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995647</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3291,6 +3421,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996049</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3402,6 +3537,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384550</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3499,6 +3639,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664474</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3596,6 +3741,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664475</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3693,6 +3843,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664476</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3790,6 +3945,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664477</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3887,6 +4047,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995604</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3984,6 +4149,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995606</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4081,6 +4251,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995607</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4178,6 +4353,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995608</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4275,6 +4455,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995609</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4372,6 +4557,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996052</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4469,6 +4659,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996053</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4575,6 +4770,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118156874</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4681,6 +4881,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118156936</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4787,6 +4992,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118156952</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4893,6 +5103,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118156977</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4999,6 +5214,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118163444</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5105,6 +5325,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118163531</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5211,6 +5436,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118163588</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5317,6 +5547,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384551</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5427,6 +5662,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117645796</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5537,6 +5777,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117646676</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5647,6 +5892,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117646699</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5757,6 +6007,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117646738</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5867,6 +6122,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117646766</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5977,6 +6237,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117646797</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6087,6 +6352,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117646835</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6197,6 +6467,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117646870</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6307,6 +6582,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117646899</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6404,6 +6684,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995630</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6501,6 +6786,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995631</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6598,6 +6888,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995633</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6695,6 +6990,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995634</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6792,6 +7092,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995635</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6889,6 +7194,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995636</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6987,6 +7297,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996057</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7084,6 +7399,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996063</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7181,6 +7501,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996064</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7278,6 +7603,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996065</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7384,6 +7714,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117662650</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7486,6 +7821,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384381</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7588,6 +7928,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384415</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7690,6 +8035,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79384609</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7787,6 +8137,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996040</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7884,6 +8239,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996041</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7981,6 +8341,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996042</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8078,6 +8443,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664469</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8176,6 +8546,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664470</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8274,6 +8649,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664471</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8372,6 +8752,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996046</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8470,6 +8855,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996047</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8568,6 +8958,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996070</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8673,6 +9068,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117659961</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8778,6 +9178,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117660195</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8883,6 +9288,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117660300</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8984,8 +9394,97 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117661399</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>